--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_PEDPRO-CSTD-0-01-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_PEDPRO-CSTD-0-01-A-C0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\ソフトチーム\20260106_REMWAR_RW\045\IpcApplication\Vom\Alert\matrix\scc\ref更新\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C69AF1-436D-4329-A8DB-3C0A72FA8BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBDBE93-9B78-4891-ABEE-893FE8E4DAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="22740" windowHeight="14070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2729" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2728" uniqueCount="319">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2661,9 +2661,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>OPT</t>
-  </si>
-  <si>
     <t>PUH_FLG</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3063,25 +3060,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>PUH_FLG = 1b を2100msecの間に2回受信で機能有無判定有りと判断</t>
-    <rPh sb="30" eb="32">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ウム</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ハンダン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>IGON15秒後
 機能有無：無</t>
     <rPh sb="14" eb="15">
@@ -3254,6 +3232,24 @@
   </si>
   <si>
     <t>－</t>
+  </si>
+  <si>
+    <t>1.4.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RWの削除
+[Config_IF]シート
+ALERT_OPT_ID_B_PEDPRO_PUH_FLG削除
+[Reference]シート
+RW記載を対象外に変更</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -4635,7 +4631,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="293">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5314,6 +5310,51 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="79" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5329,9 +5370,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5344,37 +5382,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5419,10 +5436,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5475,33 +5513,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="79" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6459,8 +6470,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="40705368" y="19173265"/>
-          <a:ext cx="16998410" cy="9663625"/>
+          <a:off x="41005125" y="19073813"/>
+          <a:ext cx="17173503" cy="9583783"/>
           <a:chOff x="40603714" y="19920857"/>
           <a:chExt cx="16918369" cy="10165489"/>
         </a:xfrm>
@@ -6552,8 +6563,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="45507088" y="6219265"/>
-          <a:ext cx="16981602" cy="11273117"/>
+          <a:off x="45862875" y="6215063"/>
+          <a:ext cx="17149690" cy="11191875"/>
           <a:chOff x="45379821" y="6300107"/>
           <a:chExt cx="16904762" cy="11851822"/>
         </a:xfrm>
@@ -13352,6 +13363,370 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AFF5100-8C8A-4071-AB53-D2FEBD305091}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15335250" y="881063"/>
+          <a:ext cx="833438" cy="6691312"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>285749</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>571498</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC817E73-743F-4A8A-866D-340ABD16A23C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16168688" y="881062"/>
+          <a:ext cx="3047999" cy="1428749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>23813</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>452437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>47624</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDDDAC4A-4AAE-486B-887D-5D0638195867}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="34837688" y="3929062"/>
+          <a:ext cx="4857749" cy="1547813"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75C2998A-E662-4718-9F73-B9B19EDE7C9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18930938" y="28241624"/>
+          <a:ext cx="20716875" cy="7000875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -13643,7 +14018,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:X13"/>
+  <dimension ref="B2:X14"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
@@ -13662,18 +14037,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="233" t="s">
+      <c r="I2" s="239" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
+      <c r="J2" s="239"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="239"/>
+      <c r="M2" s="239"/>
+      <c r="N2" s="239"/>
+      <c r="O2" s="239"/>
+      <c r="P2" s="239"/>
+      <c r="Q2" s="239"/>
+      <c r="R2" s="239"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -13686,24 +14061,24 @@
       <c r="H3" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="I3" s="234" t="s">
+      <c r="I3" s="240" t="s">
         <v>188</v>
       </c>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
-      <c r="M3" s="235"/>
-      <c r="N3" s="235"/>
-      <c r="O3" s="235"/>
-      <c r="P3" s="235"/>
-      <c r="Q3" s="235"/>
-      <c r="R3" s="235"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
+      <c r="L3" s="241"/>
+      <c r="M3" s="241"/>
+      <c r="N3" s="241"/>
+      <c r="O3" s="241"/>
+      <c r="P3" s="241"/>
+      <c r="Q3" s="241"/>
+      <c r="R3" s="241"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="21" t="str">
-        <f>DGET(B8:C14,"Ver.",H4:H5)</f>
+        <f>DGET(B8:C15,"Ver.",H4:H5)</f>
         <v>1.3.0</v>
       </c>
       <c r="F4" s="6"/>
@@ -13717,44 +14092,44 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="H5" s="11">
-        <f>MAX(B9:B14)</f>
+        <f>MAX(B9:B15)</f>
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="228" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="229"/>
-      <c r="E7" s="230" t="s">
+      <c r="C7" s="245" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="246"/>
+      <c r="E7" s="247" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="230"/>
-      <c r="G7" s="231" t="s">
+      <c r="F7" s="247"/>
+      <c r="G7" s="248" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="231"/>
-      <c r="I7" s="231"/>
-      <c r="J7" s="231"/>
-      <c r="K7" s="231"/>
-      <c r="L7" s="231"/>
-      <c r="M7" s="232" t="s">
+      <c r="H7" s="248"/>
+      <c r="I7" s="248"/>
+      <c r="J7" s="248"/>
+      <c r="K7" s="248"/>
+      <c r="L7" s="248"/>
+      <c r="M7" s="249" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="232"/>
-      <c r="O7" s="232"/>
-      <c r="P7" s="232"/>
-      <c r="Q7" s="232"/>
-      <c r="R7" s="232"/>
-      <c r="S7" s="284" t="s">
-        <v>313</v>
-      </c>
-      <c r="T7" s="285"/>
-      <c r="U7" s="285"/>
-      <c r="V7" s="285"/>
-      <c r="W7" s="285"/>
-      <c r="X7" s="286"/>
+      <c r="N7" s="249"/>
+      <c r="O7" s="249"/>
+      <c r="P7" s="249"/>
+      <c r="Q7" s="249"/>
+      <c r="R7" s="249"/>
+      <c r="S7" s="242" t="s">
+        <v>311</v>
+      </c>
+      <c r="T7" s="243"/>
+      <c r="U7" s="243"/>
+      <c r="V7" s="243"/>
+      <c r="W7" s="243"/>
+      <c r="X7" s="244"/>
     </row>
     <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
@@ -13808,8 +14183,8 @@
       <c r="R8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="S8" s="287" t="s">
-        <v>314</v>
+      <c r="S8" s="228" t="s">
+        <v>312</v>
       </c>
       <c r="T8" s="16" t="s">
         <v>7</v>
@@ -13823,7 +14198,7 @@
       <c r="W8" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="X8" s="288" t="s">
+      <c r="X8" s="229" t="s">
         <v>11</v>
       </c>
     </row>
@@ -13869,98 +14244,98 @@
       <c r="Q9" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="R9" s="292">
+      <c r="R9" s="233">
         <v>44257</v>
       </c>
-      <c r="S9" s="289" t="s">
-        <v>277</v>
+      <c r="S9" s="230" t="s">
+        <v>276</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="X9" s="290" t="s">
-        <v>277</v>
+        <v>276</v>
+      </c>
+      <c r="X9" s="231" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="2:24" ht="108">
       <c r="B10" s="9">
-        <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
+        <f t="shared" ref="B10:B14" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D10" s="217" t="s">
+        <v>295</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D10" s="217" t="s">
-        <v>296</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="N10" s="218">
         <v>44491</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P10" s="218">
         <v>44491</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="R10" s="218">
         <v>44491</v>
       </c>
-      <c r="S10" s="289" t="s">
-        <v>277</v>
+      <c r="S10" s="230" t="s">
+        <v>276</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="X10" s="49" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="2:24" ht="148.5">
@@ -13969,62 +14344,62 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D11" s="219" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="R11" s="218">
         <v>44753</v>
       </c>
-      <c r="S11" s="289" t="s">
+      <c r="S11" s="230" t="s">
         <v>130</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="X11" s="49" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="2:24" ht="40.5">
@@ -14033,109 +14408,137 @@
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D12" s="219" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="M12" s="289" t="s">
+        <v>276</v>
+      </c>
+      <c r="M12" s="230" t="s">
         <v>130</v>
       </c>
-      <c r="N12" s="289" t="s">
+      <c r="N12" s="230" t="s">
         <v>130</v>
       </c>
-      <c r="O12" s="289" t="s">
+      <c r="O12" s="230" t="s">
         <v>130</v>
       </c>
-      <c r="P12" s="289" t="s">
+      <c r="P12" s="230" t="s">
         <v>130</v>
       </c>
-      <c r="Q12" s="289" t="s">
+      <c r="Q12" s="230" t="s">
         <v>130</v>
       </c>
-      <c r="R12" s="289" t="s">
+      <c r="R12" s="230" t="s">
         <v>130</v>
       </c>
-      <c r="S12" s="289" t="s">
+      <c r="S12" s="230" t="s">
         <v>130</v>
       </c>
-      <c r="T12" s="289" t="s">
+      <c r="T12" s="230" t="s">
         <v>130</v>
       </c>
-      <c r="U12" s="289" t="s">
+      <c r="U12" s="230" t="s">
         <v>130</v>
       </c>
-      <c r="V12" s="289" t="s">
+      <c r="V12" s="230" t="s">
         <v>130</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="X12" s="216">
         <v>45978</v>
       </c>
     </row>
-    <row r="13" spans="2:24" ht="14.25" thickBot="1">
-      <c r="B13" s="9">
+    <row r="13" spans="2:24" ht="67.5">
+      <c r="C13" s="237" t="s">
+        <v>317</v>
+      </c>
+      <c r="D13" s="238" t="s">
+        <v>318</v>
+      </c>
+      <c r="E13" s="234"/>
+      <c r="F13" s="234"/>
+      <c r="G13" s="234"/>
+      <c r="H13" s="234"/>
+      <c r="I13" s="234"/>
+      <c r="J13" s="234"/>
+      <c r="K13" s="234"/>
+      <c r="L13" s="234"/>
+      <c r="M13" s="235"/>
+      <c r="N13" s="235"/>
+      <c r="O13" s="235"/>
+      <c r="P13" s="235"/>
+      <c r="Q13" s="235"/>
+      <c r="R13" s="235"/>
+      <c r="S13" s="235"/>
+      <c r="T13" s="235"/>
+      <c r="U13" s="235"/>
+      <c r="V13" s="235"/>
+      <c r="W13" s="234"/>
+      <c r="X13" s="236"/>
+    </row>
+    <row r="14" spans="2:24" ht="14.25" thickBot="1">
+      <c r="B14" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="291"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="5"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="232"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="I2:R2"/>
+    <mergeCell ref="I3:R3"/>
     <mergeCell ref="S7:X7"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="G7:L7"/>
     <mergeCell ref="M7:R7"/>
-    <mergeCell ref="I2:R2"/>
-    <mergeCell ref="I3:R3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14191,7 +14594,7 @@
         <v>144</v>
       </c>
       <c r="E8" s="127" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -14411,15 +14814,15 @@
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="236"/>
-      <c r="D38" s="237"/>
+      <c r="C38" s="250"/>
+      <c r="D38" s="251"/>
       <c r="E38" s="86" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="238"/>
-      <c r="D39" s="239"/>
+      <c r="C39" s="252"/>
+      <c r="D39" s="253"/>
       <c r="E39" s="5" t="s">
         <v>122</v>
       </c>
@@ -14460,44 +14863,44 @@
   <sheetData>
     <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="265" t="s">
+      <c r="B2" s="254" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="266"/>
-      <c r="D2" s="253" t="s">
-        <v>310</v>
-      </c>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255"/>
+      <c r="C2" s="255"/>
+      <c r="D2" s="260" t="s">
+        <v>308</v>
+      </c>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="240" t="s">
+      <c r="B3" s="256" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="241"/>
-      <c r="D3" s="256" t="s">
-        <v>311</v>
-      </c>
-      <c r="E3" s="257"/>
-      <c r="F3" s="257"/>
-      <c r="G3" s="257"/>
-      <c r="H3" s="258"/>
+      <c r="C3" s="257"/>
+      <c r="D3" s="263" t="s">
+        <v>309</v>
+      </c>
+      <c r="E3" s="264"/>
+      <c r="F3" s="264"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="265"/>
     </row>
     <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="252"/>
-      <c r="D4" s="259" t="str">
+      <c r="C4" s="259"/>
+      <c r="D4" s="266" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_PEDPRO-CSTD-0-01-A-C0.c</v>
       </c>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="261"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="268"/>
     </row>
     <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
@@ -14506,70 +14909,70 @@
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="265" t="s">
+      <c r="B6" s="254" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="266"/>
-      <c r="D6" s="262" t="str">
+      <c r="C6" s="255"/>
+      <c r="D6" s="269" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_PEDPRO</v>
       </c>
-      <c r="E6" s="263"/>
-      <c r="F6" s="263"/>
-      <c r="G6" s="263"/>
-      <c r="H6" s="264"/>
+      <c r="E6" s="270"/>
+      <c r="F6" s="270"/>
+      <c r="G6" s="270"/>
+      <c r="H6" s="271"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="240" t="s">
+      <c r="B7" s="256" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="241"/>
-      <c r="D7" s="242">
+      <c r="C7" s="257"/>
+      <c r="D7" s="272">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="243"/>
-      <c r="F7" s="243"/>
-      <c r="G7" s="243"/>
-      <c r="H7" s="244"/>
+      <c r="E7" s="273"/>
+      <c r="F7" s="273"/>
+      <c r="G7" s="273"/>
+      <c r="H7" s="274"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="240" t="s">
+      <c r="B8" s="256" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="241"/>
-      <c r="D8" s="242" t="str">
+      <c r="C8" s="257"/>
+      <c r="D8" s="272" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_PEDPRO_MTRX</v>
       </c>
-      <c r="E8" s="243"/>
-      <c r="F8" s="243"/>
-      <c r="G8" s="243"/>
-      <c r="H8" s="244"/>
+      <c r="E8" s="273"/>
+      <c r="F8" s="273"/>
+      <c r="G8" s="273"/>
+      <c r="H8" s="274"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="240" t="s">
+      <c r="B9" s="256" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="241"/>
-      <c r="D9" s="245" t="s">
-        <v>239</v>
-      </c>
-      <c r="E9" s="246"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="246"/>
-      <c r="H9" s="247"/>
+      <c r="C9" s="257"/>
+      <c r="D9" s="275" t="s">
+        <v>238</v>
+      </c>
+      <c r="E9" s="276"/>
+      <c r="F9" s="276"/>
+      <c r="G9" s="276"/>
+      <c r="H9" s="277"/>
     </row>
     <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="251" t="s">
+      <c r="B10" s="258" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="252"/>
-      <c r="D10" s="248"/>
-      <c r="E10" s="249"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="249"/>
-      <c r="H10" s="250"/>
+      <c r="C10" s="259"/>
+      <c r="D10" s="278"/>
+      <c r="E10" s="279"/>
+      <c r="F10" s="279"/>
+      <c r="G10" s="279"/>
+      <c r="H10" s="280"/>
     </row>
     <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="12" spans="2:14" ht="14.25" thickBot="1">
@@ -14615,10 +15018,10 @@
         <v>130</v>
       </c>
       <c r="D13" s="85" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E13" s="85" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F13" s="31" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
@@ -15501,22 +15904,22 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
@@ -15651,22 +16054,16 @@
       <c r="B5" s="139">
         <v>1</v>
       </c>
-      <c r="C5" s="119" t="s">
-        <v>234</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>233</v>
-      </c>
+      <c r="C5" s="119"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="47" t="str">
-        <f ca="1">IF($C5&lt;&gt;"","ALERT_" &amp; D5 &amp; "_ID_"&amp;UPPER(Matrix!$D$6) &amp; "_" &amp; $C5,"")</f>
-        <v>ALERT_OPT_ID_B_PEDPRO_PUH_FLG</v>
-      </c>
-      <c r="F5" s="90" t="s">
-        <v>297</v>
-      </c>
-      <c r="G5" s="47">
-        <f ca="1">IF(E5&lt;&gt;"",LEN(E5),"")</f>
-        <v>29</v>
+        <f>IF($C5&lt;&gt;"","ALERT_" &amp; D5 &amp; "_ID_"&amp;UPPER(Matrix!$D$6) &amp; "_" &amp; $C5,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="90"/>
+      <c r="G5" s="47" t="str">
+        <f>IF(E5&lt;&gt;"",LEN(E5),"")</f>
+        <v/>
       </c>
       <c r="O5" s="139">
         <v>1</v>
@@ -16937,19 +17334,19 @@
     </row>
     <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D4" s="87">
         <v>0</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F4" s="89" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G4" s="88" t="s">
         <v>129</v>
@@ -16958,10 +17355,10 @@
         <v>130</v>
       </c>
       <c r="I4" s="88" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J4" s="89" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K4" s="23" t="s">
         <v>129</v>
@@ -16987,10 +17384,10 @@
     </row>
     <row r="5" spans="2:21">
       <c r="B5" s="23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D5" s="90">
         <v>1</v>
@@ -16999,25 +17396,25 @@
         <v>179</v>
       </c>
       <c r="F5" s="91" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G5" s="152" t="s">
+        <v>235</v>
+      </c>
+      <c r="H5" s="91" t="s">
         <v>236</v>
-      </c>
-      <c r="H5" s="91" t="s">
-        <v>237</v>
       </c>
       <c r="I5" s="82" t="s">
         <v>179</v>
       </c>
       <c r="J5" s="91" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K5" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L5" s="91" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M5" s="26">
         <f t="shared" ref="M5:M68" ca="1" si="1">LEN(N5)</f>
@@ -17037,10 +17434,10 @@
     </row>
     <row r="6" spans="2:21">
       <c r="B6" s="23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C6" s="80" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D6" s="94">
         <v>2</v>
@@ -17049,19 +17446,19 @@
         <v>179</v>
       </c>
       <c r="F6" s="91" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G6" s="152" t="s">
+        <v>235</v>
+      </c>
+      <c r="H6" s="91" t="s">
         <v>236</v>
-      </c>
-      <c r="H6" s="91" t="s">
-        <v>237</v>
       </c>
       <c r="I6" s="152" t="s">
         <v>179</v>
       </c>
       <c r="J6" s="91" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K6" s="23" t="s">
         <v>129</v>
@@ -19598,7 +19995,7 @@
       <c r="B2" s="100" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="267" t="s">
+      <c r="C2" s="281" t="s">
         <v>81</v>
       </c>
       <c r="D2" s="37">
@@ -19697,7 +20094,7 @@
       <c r="AI2" s="37">
         <v>0</v>
       </c>
-      <c r="AJ2" s="269" t="s">
+      <c r="AJ2" s="283" t="s">
         <v>159</v>
       </c>
     </row>
@@ -19706,7 +20103,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="268"/>
+      <c r="C3" s="282"/>
       <c r="D3" s="102" t="s">
         <v>61</v>
       </c>
@@ -19791,24 +20188,24 @@
       <c r="AE3" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="AF3" s="275" t="s">
+      <c r="AF3" s="289" t="s">
+        <v>246</v>
+      </c>
+      <c r="AG3" s="290"/>
+      <c r="AH3" s="289" t="s">
         <v>247</v>
       </c>
-      <c r="AG3" s="276"/>
-      <c r="AH3" s="275" t="s">
-        <v>248</v>
-      </c>
-      <c r="AI3" s="276"/>
-      <c r="AJ3" s="270"/>
+      <c r="AI3" s="290"/>
+      <c r="AJ3" s="284"/>
       <c r="AR3" s="64" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="271" t="s">
+      <c r="A4" s="285" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="272"/>
+      <c r="B4" s="286"/>
       <c r="C4" s="112"/>
       <c r="D4" s="112"/>
       <c r="E4" s="112"/>
@@ -19853,8 +20250,8 @@
       <c r="AW4" s="54"/>
     </row>
     <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="273"/>
-      <c r="B5" s="274"/>
+      <c r="A5" s="287"/>
+      <c r="B5" s="288"/>
       <c r="C5" s="113"/>
       <c r="D5" s="113"/>
       <c r="E5" s="113"/>
@@ -20036,7 +20433,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_UNKNOWN,                                                     /* 00 UNKNOWN                                         */</v>
       </c>
       <c r="AU6" s="42" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AV6" s="27" t="s">
         <v>68</v>
@@ -20149,7 +20546,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL7" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20282,7 +20679,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AL8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20415,7 +20812,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AL9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21074,7 +21471,7 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL14" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21207,7 +21604,7 @@
         <v>1</v>
       </c>
       <c r="AJ15" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL15" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21340,7 +21737,7 @@
         <v>0</v>
       </c>
       <c r="AJ16" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL16" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21359,7 +21756,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_B_PEDPRO_DIAGDTRMN,                                          /* 10 DIAGDTRMN                                       */</v>
       </c>
       <c r="AU16" s="42" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AV16" s="28" t="s">
         <v>76</v>
@@ -21472,7 +21869,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL17" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21491,7 +21888,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_B_PEDPRO_DIAGDTRMN,                                          /* 11 DIAGDTRMN                                       */</v>
       </c>
       <c r="AU17" s="43" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AV17" s="29" t="s">
         <v>77</v>
@@ -21604,7 +22001,7 @@
         <v>0</v>
       </c>
       <c r="AJ18" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL18" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21726,7 +22123,7 @@
         <v>1</v>
       </c>
       <c r="AJ19" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL19" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21848,7 +22245,7 @@
         <v>0</v>
       </c>
       <c r="AJ20" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL20" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21970,7 +22367,7 @@
         <v>1</v>
       </c>
       <c r="AJ21" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL21" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -48395,23 +48792,23 @@
   <sheetData>
     <row r="2" spans="2:18" ht="15" thickBot="1">
       <c r="B2" s="155" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="15" thickBot="1">
       <c r="B3" s="68" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="281" t="s">
+      <c r="C3" s="295" t="s">
         <v>221</v>
       </c>
-      <c r="D3" s="282"/>
-      <c r="E3" s="282"/>
-      <c r="F3" s="282"/>
-      <c r="G3" s="282"/>
-      <c r="H3" s="282"/>
-      <c r="I3" s="282"/>
-      <c r="J3" s="283"/>
+      <c r="D3" s="296"/>
+      <c r="E3" s="296"/>
+      <c r="F3" s="296"/>
+      <c r="G3" s="296"/>
+      <c r="H3" s="296"/>
+      <c r="I3" s="296"/>
+      <c r="J3" s="297"/>
       <c r="K3" s="157"/>
       <c r="L3" s="157"/>
       <c r="M3" s="158"/>
@@ -48450,16 +48847,16 @@
       <c r="B5" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="277" t="s">
+      <c r="C5" s="291" t="s">
         <v>183</v>
       </c>
-      <c r="D5" s="278"/>
-      <c r="E5" s="278"/>
-      <c r="F5" s="278"/>
-      <c r="G5" s="278"/>
-      <c r="H5" s="278"/>
-      <c r="I5" s="278"/>
-      <c r="J5" s="279"/>
+      <c r="D5" s="292"/>
+      <c r="E5" s="292"/>
+      <c r="F5" s="292"/>
+      <c r="G5" s="292"/>
+      <c r="H5" s="292"/>
+      <c r="I5" s="292"/>
+      <c r="J5" s="293"/>
       <c r="K5" s="168" t="s">
         <v>23</v>
       </c>
@@ -48467,7 +48864,7 @@
         <v>223</v>
       </c>
       <c r="M5" s="170" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N5" s="171" t="s">
         <v>24</v>
@@ -48517,7 +48914,7 @@
         <v>99</v>
       </c>
       <c r="L6" s="175" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="M6" s="170" t="s">
         <v>220</v>
@@ -48526,41 +48923,41 @@
       <c r="O6" s="176"/>
       <c r="P6" s="177"/>
       <c r="Q6" s="222" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R6" s="222" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="27">
       <c r="B7" s="178" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="280" t="s">
+      <c r="C7" s="294" t="s">
         <v>166</v>
       </c>
-      <c r="D7" s="278"/>
-      <c r="E7" s="278"/>
-      <c r="F7" s="278"/>
-      <c r="G7" s="278"/>
-      <c r="H7" s="278"/>
-      <c r="I7" s="278"/>
-      <c r="J7" s="279"/>
+      <c r="D7" s="292"/>
+      <c r="E7" s="292"/>
+      <c r="F7" s="292"/>
+      <c r="G7" s="292"/>
+      <c r="H7" s="292"/>
+      <c r="I7" s="292"/>
+      <c r="J7" s="293"/>
       <c r="K7" s="179" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L7" s="179" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M7" s="180"/>
       <c r="N7" s="176"/>
       <c r="O7" s="176"/>
       <c r="P7" s="177"/>
       <c r="Q7" s="221" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="R7" s="221" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="2:18" ht="136.5">
@@ -48592,10 +48989,10 @@
         <v>173</v>
       </c>
       <c r="K8" s="182" t="s">
+        <v>246</v>
+      </c>
+      <c r="L8" s="182" t="s">
         <v>247</v>
-      </c>
-      <c r="L8" s="182" t="s">
-        <v>248</v>
       </c>
       <c r="M8" s="170" t="s">
         <v>30</v>
@@ -48604,10 +49001,10 @@
       <c r="O8" s="176"/>
       <c r="P8" s="177"/>
       <c r="Q8" s="221" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R8" s="221" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="2:18" ht="95.25" thickBot="1">
@@ -48642,28 +49039,28 @@
         <v>222</v>
       </c>
       <c r="L9" s="185" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="M9" s="186" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N9" s="187" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O9" s="188" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P9" s="189"/>
       <c r="Q9" s="223" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="R9" s="223" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="2:18" ht="14.25" thickTop="1">
       <c r="B10" s="190" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C10" s="191" t="s">
         <v>174</v>
@@ -48699,22 +49096,22 @@
         <v>232</v>
       </c>
       <c r="N10" s="194" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O10" s="195" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P10" s="196"/>
       <c r="Q10" s="224" t="s">
         <v>130</v>
       </c>
       <c r="R10" s="224" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="2:18">
       <c r="B11" s="197" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C11" s="198" t="s">
         <v>174</v>
@@ -48747,17 +49144,17 @@
         <v>227</v>
       </c>
       <c r="M11" s="200" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N11" s="201" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O11" s="202" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P11" s="203"/>
       <c r="Q11" s="225" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R11" s="225" t="s">
         <v>130</v>
@@ -48765,7 +49162,7 @@
     </row>
     <row r="12" spans="2:18">
       <c r="B12" s="197" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C12" s="198" t="s">
         <v>174</v>
@@ -48798,25 +49195,25 @@
         <v>229</v>
       </c>
       <c r="M12" s="200" t="s">
+        <v>273</v>
+      </c>
+      <c r="N12" s="201" t="s">
         <v>274</v>
       </c>
-      <c r="N12" s="201" t="s">
-        <v>275</v>
-      </c>
       <c r="O12" s="202" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P12" s="203"/>
       <c r="Q12" s="225" t="s">
         <v>130</v>
       </c>
       <c r="R12" s="225" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="2:18">
       <c r="B13" s="197" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C13" s="198" t="s">
         <v>174</v>
@@ -48849,25 +49246,25 @@
         <v>231</v>
       </c>
       <c r="M13" s="200" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N13" s="201" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O13" s="202" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P13" s="203"/>
       <c r="Q13" s="225" t="s">
         <v>130</v>
       </c>
       <c r="R13" s="225" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="2:18">
       <c r="B14" s="197" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C14" s="198" t="s">
         <v>174</v>
@@ -48903,10 +49300,10 @@
         <v>32</v>
       </c>
       <c r="N14" s="201" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O14" s="202" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P14" s="203"/>
       <c r="Q14" s="225" t="s">
@@ -48918,7 +49315,7 @@
     </row>
     <row r="15" spans="2:18">
       <c r="B15" s="197" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C15" s="198" t="s">
         <v>174</v>
@@ -48954,10 +49351,10 @@
         <v>32</v>
       </c>
       <c r="N15" s="201" t="s">
+        <v>276</v>
+      </c>
+      <c r="O15" s="202" t="s">
         <v>277</v>
-      </c>
-      <c r="O15" s="202" t="s">
-        <v>278</v>
       </c>
       <c r="P15" s="203"/>
       <c r="Q15" s="225" t="s">
@@ -48969,7 +49366,7 @@
     </row>
     <row r="16" spans="2:18">
       <c r="B16" s="197" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C16" s="198" t="s">
         <v>174</v>
@@ -49005,10 +49402,10 @@
         <v>32</v>
       </c>
       <c r="N16" s="201" t="s">
+        <v>276</v>
+      </c>
+      <c r="O16" s="202" t="s">
         <v>277</v>
-      </c>
-      <c r="O16" s="202" t="s">
-        <v>278</v>
       </c>
       <c r="P16" s="203"/>
       <c r="Q16" s="225" t="s">
@@ -49020,7 +49417,7 @@
     </row>
     <row r="17" spans="2:18">
       <c r="B17" s="197" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C17" s="198" t="s">
         <v>174</v>
@@ -49056,10 +49453,10 @@
         <v>32</v>
       </c>
       <c r="N17" s="201" t="s">
+        <v>276</v>
+      </c>
+      <c r="O17" s="202" t="s">
         <v>277</v>
-      </c>
-      <c r="O17" s="202" t="s">
-        <v>278</v>
       </c>
       <c r="P17" s="203"/>
       <c r="Q17" s="225" t="s">
@@ -49071,7 +49468,7 @@
     </row>
     <row r="18" spans="2:18">
       <c r="B18" s="197" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C18" s="204" t="s">
         <v>174</v>
@@ -49104,17 +49501,17 @@
         <v>224</v>
       </c>
       <c r="M18" s="200" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N18" s="206" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O18" s="154" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P18" s="207"/>
       <c r="Q18" s="226" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R18" s="225" t="s">
         <v>130</v>
@@ -49122,7 +49519,7 @@
     </row>
     <row r="19" spans="2:18">
       <c r="B19" s="197" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C19" s="198" t="s">
         <v>174</v>
@@ -49155,17 +49552,17 @@
         <v>226</v>
       </c>
       <c r="M19" s="200" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N19" s="201" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O19" s="154" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P19" s="203"/>
       <c r="Q19" s="226" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R19" s="225" t="s">
         <v>130</v>
@@ -49173,7 +49570,7 @@
     </row>
     <row r="20" spans="2:18">
       <c r="B20" s="197" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C20" s="204" t="s">
         <v>174</v>
@@ -49206,17 +49603,17 @@
         <v>228</v>
       </c>
       <c r="M20" s="200" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N20" s="206" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O20" s="154" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P20" s="207"/>
       <c r="Q20" s="226" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R20" s="225" t="s">
         <v>130</v>
@@ -49224,7 +49621,7 @@
     </row>
     <row r="21" spans="2:18">
       <c r="B21" s="197" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C21" s="198" t="s">
         <v>174</v>
@@ -49257,17 +49654,17 @@
         <v>230</v>
       </c>
       <c r="M21" s="200" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N21" s="201" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O21" s="154" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P21" s="203"/>
       <c r="Q21" s="226" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R21" s="225" t="s">
         <v>130</v>
@@ -49275,7 +49672,7 @@
     </row>
     <row r="22" spans="2:18">
       <c r="B22" s="197" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C22" s="204" t="s">
         <v>174</v>
@@ -49308,17 +49705,17 @@
         <v>224</v>
       </c>
       <c r="M22" s="200" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N22" s="201" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O22" s="154" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P22" s="203"/>
       <c r="Q22" s="226" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R22" s="225" t="s">
         <v>130</v>
@@ -49326,7 +49723,7 @@
     </row>
     <row r="23" spans="2:18">
       <c r="B23" s="197" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C23" s="198" t="s">
         <v>174</v>
@@ -49359,17 +49756,17 @@
         <v>226</v>
       </c>
       <c r="M23" s="200" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N23" s="201" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O23" s="154" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P23" s="203"/>
       <c r="Q23" s="226" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R23" s="225" t="s">
         <v>130</v>
@@ -49377,7 +49774,7 @@
     </row>
     <row r="24" spans="2:18">
       <c r="B24" s="197" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C24" s="204" t="s">
         <v>174</v>
@@ -49410,17 +49807,17 @@
         <v>228</v>
       </c>
       <c r="M24" s="200" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N24" s="201" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O24" s="154" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P24" s="203"/>
       <c r="Q24" s="226" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R24" s="225" t="s">
         <v>130</v>
@@ -49428,7 +49825,7 @@
     </row>
     <row r="25" spans="2:18">
       <c r="B25" s="197" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C25" s="198" t="s">
         <v>174</v>
@@ -49461,17 +49858,17 @@
         <v>230</v>
       </c>
       <c r="M25" s="200" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N25" s="201" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O25" s="154" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P25" s="203"/>
       <c r="Q25" s="226" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R25" s="225" t="s">
         <v>130</v>
@@ -49479,7 +49876,7 @@
     </row>
     <row r="26" spans="2:18" ht="14.25" thickBot="1">
       <c r="B26" s="208" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C26" s="209" t="s">
         <v>174</v>
@@ -49506,26 +49903,26 @@
         <v>174</v>
       </c>
       <c r="K26" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L26" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M26" s="212" t="s">
         <v>32</v>
       </c>
       <c r="N26" s="213" t="s">
+        <v>276</v>
+      </c>
+      <c r="O26" s="214" t="s">
         <v>277</v>
-      </c>
-      <c r="O26" s="214" t="s">
-        <v>278</v>
       </c>
       <c r="P26" s="215"/>
       <c r="Q26" s="227" t="s">
         <v>130</v>
       </c>
       <c r="R26" s="227" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -49806,10 +50203,10 @@
         <v>20</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D24" s="62" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="2:4">
